--- a/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
+++ b/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munoz\Desktop\Fase 1\Fase uno\Documentacion Scrum\Product backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1FB61B-5358-4A37-9504-17AA8A2ECA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02920EA6-059E-4958-8CE0-BBB3D5BB14C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEE2A4FB-0BE4-4EA1-8CAE-95F0BC4AD543}"/>
   </bookViews>
@@ -513,9 +513,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -523,6 +520,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -959,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AFFAA47-E17C-4B8F-9C68-1593413A7371}">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
@@ -979,38 +979,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:13" s="6" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21"/>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="20"/>
+      <c r="B2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="4"/>
@@ -1036,7 +1036,7 @@
         <v>45894</v>
       </c>
       <c r="E3" s="9">
-        <v>45922</v>
+        <v>45905</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>43</v>

--- a/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
+++ b/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munoz\Desktop\Fase 1\Fase uno\Documentacion Scrum\Product backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02920EA6-059E-4958-8CE0-BBB3D5BB14C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65195121-D39B-4F0C-B210-DBE7C3F4A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEE2A4FB-0BE4-4EA1-8CAE-95F0BC4AD543}"/>
   </bookViews>

--- a/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
+++ b/Fase uno/Documentacion Scrum/Product backlog/Product Backlog Prirorizado SOC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munoz\Desktop\Fase 1\Fase uno\Documentacion Scrum\Product backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65195121-D39B-4F0C-B210-DBE7C3F4A83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1087B418-F995-4118-A001-A1730CFCCC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EEE2A4FB-0BE4-4EA1-8CAE-95F0BC4AD543}"/>
   </bookViews>
